--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467398</v>
+        <v>121467388</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455487</v>
+        <v>455401</v>
       </c>
       <c r="R2" t="n">
-        <v>7045465</v>
+        <v>7045452</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467372</v>
+        <v>121467387</v>
       </c>
       <c r="B3" t="n">
         <v>57351</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455187</v>
+        <v>455393</v>
       </c>
       <c r="R3" t="n">
-        <v>7045215</v>
+        <v>7045474</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467391</v>
+        <v>121467425</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455423</v>
+        <v>455347</v>
       </c>
       <c r="R4" t="n">
-        <v>7045462</v>
+        <v>7045381</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467374</v>
+        <v>121467372</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455215</v>
+        <v>455187</v>
       </c>
       <c r="R5" t="n">
-        <v>7045221</v>
+        <v>7045215</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467375</v>
+        <v>121467368</v>
       </c>
       <c r="B6" t="n">
         <v>57351</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455210</v>
+        <v>455177</v>
       </c>
       <c r="R6" t="n">
-        <v>7045219</v>
+        <v>7045186</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467360</v>
+        <v>121467398</v>
       </c>
       <c r="B7" t="n">
-        <v>90709</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455351</v>
+        <v>455487</v>
       </c>
       <c r="R7" t="n">
-        <v>7045479</v>
+        <v>7045465</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467377</v>
+        <v>121467385</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455205</v>
+        <v>455288</v>
       </c>
       <c r="R8" t="n">
-        <v>7045318</v>
+        <v>7045273</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467394</v>
+        <v>121467369</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455431</v>
+        <v>455191</v>
       </c>
       <c r="R9" t="n">
-        <v>7045439</v>
+        <v>7045208</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467361</v>
+        <v>121467396</v>
       </c>
       <c r="B10" t="n">
-        <v>90709</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455338</v>
+        <v>455447</v>
       </c>
       <c r="R10" t="n">
-        <v>7045372</v>
+        <v>7045445</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467369</v>
+        <v>121467382</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455191</v>
+        <v>455331</v>
       </c>
       <c r="R11" t="n">
-        <v>7045208</v>
+        <v>7045475</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467388</v>
+        <v>121467379</v>
       </c>
       <c r="B12" t="n">
         <v>57351</v>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455401</v>
+        <v>455254</v>
       </c>
       <c r="R12" t="n">
-        <v>7045452</v>
+        <v>7045408</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467380</v>
+        <v>121467378</v>
       </c>
       <c r="B13" t="n">
         <v>57351</v>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455268</v>
+        <v>455092</v>
       </c>
       <c r="R13" t="n">
-        <v>7045458</v>
+        <v>7045431</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467385</v>
+        <v>121467381</v>
       </c>
       <c r="B14" t="n">
         <v>57351</v>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455288</v>
+        <v>455305</v>
       </c>
       <c r="R14" t="n">
-        <v>7045273</v>
+        <v>7045497</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467393</v>
+        <v>121467384</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455424</v>
+        <v>455325</v>
       </c>
       <c r="R15" t="n">
-        <v>7045452</v>
+        <v>7045474</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467368</v>
+        <v>121467386</v>
       </c>
       <c r="B16" t="n">
         <v>57351</v>
@@ -2203,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455177</v>
+        <v>455349</v>
       </c>
       <c r="R16" t="n">
-        <v>7045186</v>
+        <v>7045416</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467379</v>
+        <v>121467427</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455254</v>
+        <v>455363</v>
       </c>
       <c r="R17" t="n">
-        <v>7045408</v>
+        <v>7045446</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,11 +2351,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467390</v>
+        <v>121467380</v>
       </c>
       <c r="B18" t="n">
         <v>57351</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455426</v>
+        <v>455268</v>
       </c>
       <c r="R18" t="n">
-        <v>7045466</v>
+        <v>7045458</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467423</v>
+        <v>121467377</v>
       </c>
       <c r="B19" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,16 +2500,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455053</v>
+        <v>455205</v>
       </c>
       <c r="R19" t="n">
-        <v>7045436</v>
+        <v>7045318</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467370</v>
+        <v>121467394</v>
       </c>
       <c r="B20" t="n">
         <v>57351</v>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455184</v>
+        <v>455431</v>
       </c>
       <c r="R20" t="n">
-        <v>7045212</v>
+        <v>7045439</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467382</v>
+        <v>121467360</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>90709</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455331</v>
+        <v>455351</v>
       </c>
       <c r="R21" t="n">
-        <v>7045475</v>
+        <v>7045479</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,11 +2774,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2800,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467387</v>
+        <v>121467374</v>
       </c>
       <c r="B22" t="n">
         <v>57351</v>
@@ -2845,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455393</v>
+        <v>455215</v>
       </c>
       <c r="R22" t="n">
-        <v>7045474</v>
+        <v>7045221</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467381</v>
+        <v>121467390</v>
       </c>
       <c r="B23" t="n">
         <v>57351</v>
@@ -2952,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455305</v>
+        <v>455426</v>
       </c>
       <c r="R23" t="n">
-        <v>7045497</v>
+        <v>7045466</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467397</v>
+        <v>121467375</v>
       </c>
       <c r="B24" t="n">
         <v>57351</v>
@@ -3059,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455478</v>
+        <v>455210</v>
       </c>
       <c r="R24" t="n">
-        <v>7045446</v>
+        <v>7045219</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3094,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467378</v>
+        <v>121467361</v>
       </c>
       <c r="B25" t="n">
-        <v>57351</v>
+        <v>90709</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,21 +3137,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455092</v>
+        <v>455338</v>
       </c>
       <c r="R25" t="n">
-        <v>7045431</v>
+        <v>7045372</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,11 +3197,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,7 +3223,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467384</v>
+        <v>121467393</v>
       </c>
       <c r="B26" t="n">
         <v>57351</v>
@@ -3273,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455325</v>
+        <v>455424</v>
       </c>
       <c r="R26" t="n">
-        <v>7045474</v>
+        <v>7045452</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3340,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467386</v>
+        <v>121467423</v>
       </c>
       <c r="B27" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3356,16 +3346,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3380,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455349</v>
+        <v>455053</v>
       </c>
       <c r="R27" t="n">
-        <v>7045416</v>
+        <v>7045436</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467427</v>
+        <v>121467391</v>
       </c>
       <c r="B28" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,21 +3453,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3487,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455363</v>
+        <v>455423</v>
       </c>
       <c r="R28" t="n">
-        <v>7045446</v>
+        <v>7045462</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3523,6 +3513,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467425</v>
+        <v>121467370</v>
       </c>
       <c r="B29" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,21 +3560,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455347</v>
+        <v>455184</v>
       </c>
       <c r="R29" t="n">
-        <v>7045381</v>
+        <v>7045212</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3625,6 +3620,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467396</v>
+        <v>121467397</v>
       </c>
       <c r="B30" t="n">
         <v>57351</v>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455447</v>
+        <v>455478</v>
       </c>
       <c r="R30" t="n">
-        <v>7045445</v>
+        <v>7045446</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467388</v>
+        <v>121467386</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455401</v>
+        <v>455349</v>
       </c>
       <c r="R2" t="n">
-        <v>7045452</v>
+        <v>7045416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467387</v>
+        <v>121467394</v>
       </c>
       <c r="B3" t="n">
         <v>57351</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455393</v>
+        <v>455431</v>
       </c>
       <c r="R3" t="n">
-        <v>7045474</v>
+        <v>7045439</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467425</v>
+        <v>121467369</v>
       </c>
       <c r="B4" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455347</v>
+        <v>455191</v>
       </c>
       <c r="R4" t="n">
-        <v>7045381</v>
+        <v>7045208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467372</v>
+        <v>121467360</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>90710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455187</v>
+        <v>455351</v>
       </c>
       <c r="R5" t="n">
-        <v>7045215</v>
+        <v>7045479</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467368</v>
+        <v>121467425</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455177</v>
+        <v>455347</v>
       </c>
       <c r="R6" t="n">
-        <v>7045186</v>
+        <v>7045381</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467398</v>
+        <v>121467379</v>
       </c>
       <c r="B7" t="n">
         <v>57351</v>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455487</v>
+        <v>455254</v>
       </c>
       <c r="R7" t="n">
-        <v>7045465</v>
+        <v>7045408</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467385</v>
+        <v>121467396</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455288</v>
+        <v>455447</v>
       </c>
       <c r="R8" t="n">
-        <v>7045273</v>
+        <v>7045445</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467369</v>
+        <v>121467381</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455191</v>
+        <v>455305</v>
       </c>
       <c r="R9" t="n">
-        <v>7045208</v>
+        <v>7045497</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467396</v>
+        <v>121467384</v>
       </c>
       <c r="B10" t="n">
         <v>57351</v>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455447</v>
+        <v>455325</v>
       </c>
       <c r="R10" t="n">
-        <v>7045445</v>
+        <v>7045474</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467382</v>
+        <v>121467368</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455331</v>
+        <v>455177</v>
       </c>
       <c r="R11" t="n">
-        <v>7045475</v>
+        <v>7045186</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467379</v>
+        <v>121467374</v>
       </c>
       <c r="B12" t="n">
         <v>57351</v>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455254</v>
+        <v>455215</v>
       </c>
       <c r="R12" t="n">
-        <v>7045408</v>
+        <v>7045221</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467378</v>
+        <v>121467391</v>
       </c>
       <c r="B13" t="n">
         <v>57351</v>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455092</v>
+        <v>455423</v>
       </c>
       <c r="R13" t="n">
-        <v>7045431</v>
+        <v>7045462</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467381</v>
+        <v>121467385</v>
       </c>
       <c r="B14" t="n">
         <v>57351</v>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455305</v>
+        <v>455288</v>
       </c>
       <c r="R14" t="n">
-        <v>7045497</v>
+        <v>7045273</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467384</v>
+        <v>121467387</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2101,7 +2096,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455325</v>
+        <v>455393</v>
       </c>
       <c r="R15" t="n">
         <v>7045474</v>
@@ -2168,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467386</v>
+        <v>121467423</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,16 +2179,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455349</v>
+        <v>455053</v>
       </c>
       <c r="R16" t="n">
-        <v>7045416</v>
+        <v>7045436</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467427</v>
+        <v>121467390</v>
       </c>
       <c r="B17" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455363</v>
+        <v>455426</v>
       </c>
       <c r="R17" t="n">
-        <v>7045446</v>
+        <v>7045466</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2346,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467380</v>
+        <v>121467397</v>
       </c>
       <c r="B18" t="n">
         <v>57351</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455268</v>
+        <v>455478</v>
       </c>
       <c r="R18" t="n">
-        <v>7045458</v>
+        <v>7045446</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467377</v>
+        <v>121467427</v>
       </c>
       <c r="B19" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2500,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455205</v>
+        <v>455363</v>
       </c>
       <c r="R19" t="n">
-        <v>7045318</v>
+        <v>7045446</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467394</v>
+        <v>121467377</v>
       </c>
       <c r="B20" t="n">
         <v>57351</v>
@@ -2631,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455431</v>
+        <v>455205</v>
       </c>
       <c r="R20" t="n">
-        <v>7045439</v>
+        <v>7045318</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467360</v>
+        <v>121467361</v>
       </c>
       <c r="B21" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2738,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455351</v>
+        <v>455338</v>
       </c>
       <c r="R21" t="n">
-        <v>7045479</v>
+        <v>7045372</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467374</v>
+        <v>121467370</v>
       </c>
       <c r="B22" t="n">
         <v>57351</v>
@@ -2840,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455215</v>
+        <v>455184</v>
       </c>
       <c r="R22" t="n">
-        <v>7045221</v>
+        <v>7045212</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467390</v>
+        <v>121467378</v>
       </c>
       <c r="B23" t="n">
         <v>57351</v>
@@ -2947,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455426</v>
+        <v>455092</v>
       </c>
       <c r="R23" t="n">
-        <v>7045466</v>
+        <v>7045431</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467375</v>
+        <v>121467398</v>
       </c>
       <c r="B24" t="n">
         <v>57351</v>
@@ -3054,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455210</v>
+        <v>455487</v>
       </c>
       <c r="R24" t="n">
-        <v>7045219</v>
+        <v>7045465</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467361</v>
+        <v>121467380</v>
       </c>
       <c r="B25" t="n">
-        <v>90709</v>
+        <v>57351</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455338</v>
+        <v>455268</v>
       </c>
       <c r="R25" t="n">
-        <v>7045372</v>
+        <v>7045458</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,6 +3192,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467423</v>
+        <v>121467375</v>
       </c>
       <c r="B27" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3346,16 +3346,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455053</v>
+        <v>455210</v>
       </c>
       <c r="R27" t="n">
-        <v>7045436</v>
+        <v>7045219</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,7 +3437,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467391</v>
+        <v>121467382</v>
       </c>
       <c r="B28" t="n">
         <v>57351</v>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455423</v>
+        <v>455331</v>
       </c>
       <c r="R28" t="n">
-        <v>7045462</v>
+        <v>7045475</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467370</v>
+        <v>121467372</v>
       </c>
       <c r="B29" t="n">
         <v>57351</v>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455184</v>
+        <v>455187</v>
       </c>
       <c r="R29" t="n">
-        <v>7045212</v>
+        <v>7045215</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467397</v>
+        <v>121467388</v>
       </c>
       <c r="B30" t="n">
         <v>57351</v>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455478</v>
+        <v>455401</v>
       </c>
       <c r="R30" t="n">
-        <v>7045446</v>
+        <v>7045452</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467386</v>
+        <v>121467425</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455349</v>
+        <v>455347</v>
       </c>
       <c r="R2" t="n">
-        <v>7045416</v>
+        <v>7045381</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467394</v>
+        <v>121467385</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455431</v>
+        <v>455288</v>
       </c>
       <c r="R3" t="n">
-        <v>7045439</v>
+        <v>7045273</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467369</v>
+        <v>121467360</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>90713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455191</v>
+        <v>455351</v>
       </c>
       <c r="R4" t="n">
-        <v>7045208</v>
+        <v>7045479</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467360</v>
+        <v>121467423</v>
       </c>
       <c r="B5" t="n">
-        <v>90710</v>
+        <v>57370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455351</v>
+        <v>455053</v>
       </c>
       <c r="R5" t="n">
-        <v>7045479</v>
+        <v>7045436</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467425</v>
+        <v>121467375</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455347</v>
+        <v>455210</v>
       </c>
       <c r="R6" t="n">
-        <v>7045381</v>
+        <v>7045219</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467379</v>
+        <v>121467378</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455254</v>
+        <v>455092</v>
       </c>
       <c r="R7" t="n">
-        <v>7045408</v>
+        <v>7045431</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467396</v>
+        <v>121467369</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455447</v>
+        <v>455191</v>
       </c>
       <c r="R8" t="n">
-        <v>7045445</v>
+        <v>7045208</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467381</v>
+        <v>121467388</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455305</v>
+        <v>455401</v>
       </c>
       <c r="R9" t="n">
-        <v>7045497</v>
+        <v>7045452</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467384</v>
+        <v>121467397</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455325</v>
+        <v>455478</v>
       </c>
       <c r="R10" t="n">
-        <v>7045474</v>
+        <v>7045446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467368</v>
+        <v>121467427</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>90731</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455177</v>
+        <v>455363</v>
       </c>
       <c r="R11" t="n">
-        <v>7045186</v>
+        <v>7045446</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467374</v>
+        <v>121467380</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455215</v>
+        <v>455268</v>
       </c>
       <c r="R12" t="n">
-        <v>7045221</v>
+        <v>7045458</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467391</v>
+        <v>121467390</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455423</v>
+        <v>455426</v>
       </c>
       <c r="R13" t="n">
-        <v>7045462</v>
+        <v>7045466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467385</v>
+        <v>121467374</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455288</v>
+        <v>455215</v>
       </c>
       <c r="R14" t="n">
-        <v>7045273</v>
+        <v>7045221</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467387</v>
+        <v>121467379</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455393</v>
+        <v>455254</v>
       </c>
       <c r="R15" t="n">
-        <v>7045474</v>
+        <v>7045408</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467423</v>
+        <v>121467391</v>
       </c>
       <c r="B16" t="n">
-        <v>57367</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,16 +2174,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455053</v>
+        <v>455423</v>
       </c>
       <c r="R16" t="n">
-        <v>7045436</v>
+        <v>7045462</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2238,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467390</v>
+        <v>121467368</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455426</v>
+        <v>455177</v>
       </c>
       <c r="R17" t="n">
-        <v>7045466</v>
+        <v>7045186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2345,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467397</v>
+        <v>121467377</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455478</v>
+        <v>455205</v>
       </c>
       <c r="R18" t="n">
-        <v>7045446</v>
+        <v>7045318</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467427</v>
+        <v>121467382</v>
       </c>
       <c r="B19" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455363</v>
+        <v>455331</v>
       </c>
       <c r="R19" t="n">
-        <v>7045446</v>
+        <v>7045475</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,6 +2555,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467377</v>
+        <v>121467398</v>
       </c>
       <c r="B20" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455205</v>
+        <v>455487</v>
       </c>
       <c r="R20" t="n">
-        <v>7045318</v>
+        <v>7045465</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467361</v>
+        <v>121467381</v>
       </c>
       <c r="B21" t="n">
-        <v>90710</v>
+        <v>57354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455338</v>
+        <v>455305</v>
       </c>
       <c r="R21" t="n">
-        <v>7045372</v>
+        <v>7045497</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,6 +2769,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467370</v>
+        <v>121467394</v>
       </c>
       <c r="B22" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2835,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455184</v>
+        <v>455431</v>
       </c>
       <c r="R22" t="n">
-        <v>7045212</v>
+        <v>7045439</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2902,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467378</v>
+        <v>121467393</v>
       </c>
       <c r="B23" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455092</v>
+        <v>455424</v>
       </c>
       <c r="R23" t="n">
-        <v>7045431</v>
+        <v>7045452</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467398</v>
+        <v>121467387</v>
       </c>
       <c r="B24" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3049,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455487</v>
+        <v>455393</v>
       </c>
       <c r="R24" t="n">
-        <v>7045465</v>
+        <v>7045474</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467380</v>
+        <v>121467372</v>
       </c>
       <c r="B25" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3156,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455268</v>
+        <v>455187</v>
       </c>
       <c r="R25" t="n">
-        <v>7045458</v>
+        <v>7045215</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3223,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467393</v>
+        <v>121467370</v>
       </c>
       <c r="B26" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455424</v>
+        <v>455184</v>
       </c>
       <c r="R26" t="n">
-        <v>7045452</v>
+        <v>7045212</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467375</v>
+        <v>121467361</v>
       </c>
       <c r="B27" t="n">
-        <v>57351</v>
+        <v>90713</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3346,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455210</v>
+        <v>455338</v>
       </c>
       <c r="R27" t="n">
-        <v>7045219</v>
+        <v>7045372</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,11 +3411,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467382</v>
+        <v>121467396</v>
       </c>
       <c r="B28" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455331</v>
+        <v>455447</v>
       </c>
       <c r="R28" t="n">
-        <v>7045475</v>
+        <v>7045445</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467372</v>
+        <v>121467386</v>
       </c>
       <c r="B29" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455187</v>
+        <v>455349</v>
       </c>
       <c r="R29" t="n">
-        <v>7045215</v>
+        <v>7045416</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467388</v>
+        <v>121467384</v>
       </c>
       <c r="B30" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455401</v>
+        <v>455325</v>
       </c>
       <c r="R30" t="n">
-        <v>7045452</v>
+        <v>7045474</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467425</v>
+        <v>121467380</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455347</v>
+        <v>455268</v>
       </c>
       <c r="R2" t="n">
-        <v>7045381</v>
+        <v>7045458</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467385</v>
+        <v>121467396</v>
       </c>
       <c r="B3" t="n">
         <v>57354</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455288</v>
+        <v>455447</v>
       </c>
       <c r="R3" t="n">
-        <v>7045273</v>
+        <v>7045445</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467360</v>
+        <v>121467397</v>
       </c>
       <c r="B4" t="n">
-        <v>90713</v>
+        <v>57354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455351</v>
+        <v>455478</v>
       </c>
       <c r="R4" t="n">
-        <v>7045479</v>
+        <v>7045446</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467423</v>
+        <v>121467385</v>
       </c>
       <c r="B5" t="n">
-        <v>57370</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,16 +1012,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455053</v>
+        <v>455288</v>
       </c>
       <c r="R5" t="n">
-        <v>7045436</v>
+        <v>7045273</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467375</v>
+        <v>121467378</v>
       </c>
       <c r="B6" t="n">
         <v>57354</v>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455210</v>
+        <v>455092</v>
       </c>
       <c r="R6" t="n">
-        <v>7045219</v>
+        <v>7045431</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467378</v>
+        <v>121467379</v>
       </c>
       <c r="B7" t="n">
         <v>57354</v>
@@ -1240,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455092</v>
+        <v>455254</v>
       </c>
       <c r="R7" t="n">
-        <v>7045431</v>
+        <v>7045408</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467369</v>
+        <v>121467377</v>
       </c>
       <c r="B8" t="n">
         <v>57354</v>
@@ -1347,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455191</v>
+        <v>455205</v>
       </c>
       <c r="R8" t="n">
-        <v>7045208</v>
+        <v>7045318</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467388</v>
+        <v>121467391</v>
       </c>
       <c r="B9" t="n">
         <v>57354</v>
@@ -1454,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455401</v>
+        <v>455423</v>
       </c>
       <c r="R9" t="n">
-        <v>7045452</v>
+        <v>7045462</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467397</v>
+        <v>121467388</v>
       </c>
       <c r="B10" t="n">
         <v>57354</v>
@@ -1561,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455478</v>
+        <v>455401</v>
       </c>
       <c r="R10" t="n">
-        <v>7045446</v>
+        <v>7045452</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467427</v>
+        <v>121467387</v>
       </c>
       <c r="B11" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455363</v>
+        <v>455393</v>
       </c>
       <c r="R11" t="n">
-        <v>7045446</v>
+        <v>7045474</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1714,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467380</v>
+        <v>121467381</v>
       </c>
       <c r="B12" t="n">
         <v>57354</v>
@@ -1770,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455268</v>
+        <v>455305</v>
       </c>
       <c r="R12" t="n">
-        <v>7045458</v>
+        <v>7045497</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467390</v>
+        <v>121467427</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455426</v>
+        <v>455363</v>
       </c>
       <c r="R13" t="n">
-        <v>7045466</v>
+        <v>7045446</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,11 +1928,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467374</v>
+        <v>121467393</v>
       </c>
       <c r="B14" t="n">
         <v>57354</v>
@@ -1984,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455215</v>
+        <v>455424</v>
       </c>
       <c r="R14" t="n">
-        <v>7045221</v>
+        <v>7045452</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467379</v>
+        <v>121467398</v>
       </c>
       <c r="B15" t="n">
         <v>57354</v>
@@ -2091,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455254</v>
+        <v>455487</v>
       </c>
       <c r="R15" t="n">
-        <v>7045408</v>
+        <v>7045465</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467391</v>
+        <v>121467382</v>
       </c>
       <c r="B16" t="n">
         <v>57354</v>
@@ -2198,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455423</v>
+        <v>455331</v>
       </c>
       <c r="R16" t="n">
-        <v>7045462</v>
+        <v>7045475</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467368</v>
+        <v>121467390</v>
       </c>
       <c r="B17" t="n">
         <v>57354</v>
@@ -2305,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455177</v>
+        <v>455426</v>
       </c>
       <c r="R17" t="n">
-        <v>7045186</v>
+        <v>7045466</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467377</v>
+        <v>121467425</v>
       </c>
       <c r="B18" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455205</v>
+        <v>455347</v>
       </c>
       <c r="R18" t="n">
-        <v>7045318</v>
+        <v>7045381</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,11 +2458,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467382</v>
+        <v>121467370</v>
       </c>
       <c r="B19" t="n">
         <v>57354</v>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455331</v>
+        <v>455184</v>
       </c>
       <c r="R19" t="n">
-        <v>7045475</v>
+        <v>7045212</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467398</v>
+        <v>121467374</v>
       </c>
       <c r="B20" t="n">
         <v>57354</v>
@@ -2626,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455487</v>
+        <v>455215</v>
       </c>
       <c r="R20" t="n">
-        <v>7045465</v>
+        <v>7045221</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467381</v>
+        <v>121467372</v>
       </c>
       <c r="B21" t="n">
         <v>57354</v>
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455305</v>
+        <v>455187</v>
       </c>
       <c r="R21" t="n">
-        <v>7045497</v>
+        <v>7045215</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467394</v>
+        <v>121467384</v>
       </c>
       <c r="B22" t="n">
         <v>57354</v>
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455431</v>
+        <v>455325</v>
       </c>
       <c r="R22" t="n">
-        <v>7045439</v>
+        <v>7045474</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467393</v>
+        <v>121467361</v>
       </c>
       <c r="B23" t="n">
-        <v>57354</v>
+        <v>90713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2928,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455424</v>
+        <v>455338</v>
       </c>
       <c r="R23" t="n">
-        <v>7045452</v>
+        <v>7045372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,11 +2988,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467387</v>
+        <v>121467369</v>
       </c>
       <c r="B24" t="n">
         <v>57354</v>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455393</v>
+        <v>455191</v>
       </c>
       <c r="R24" t="n">
-        <v>7045474</v>
+        <v>7045208</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467372</v>
+        <v>121467394</v>
       </c>
       <c r="B25" t="n">
         <v>57354</v>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455187</v>
+        <v>455431</v>
       </c>
       <c r="R25" t="n">
-        <v>7045215</v>
+        <v>7045439</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467370</v>
+        <v>121467423</v>
       </c>
       <c r="B26" t="n">
-        <v>57354</v>
+        <v>57370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,16 +3244,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455184</v>
+        <v>455053</v>
       </c>
       <c r="R26" t="n">
-        <v>7045212</v>
+        <v>7045436</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467361</v>
+        <v>121467375</v>
       </c>
       <c r="B27" t="n">
-        <v>90713</v>
+        <v>57354</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455338</v>
+        <v>455210</v>
       </c>
       <c r="R27" t="n">
-        <v>7045372</v>
+        <v>7045219</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,6 +3411,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467396</v>
+        <v>121467360</v>
       </c>
       <c r="B28" t="n">
-        <v>57354</v>
+        <v>90713</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3453,21 +3458,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3477,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455447</v>
+        <v>455351</v>
       </c>
       <c r="R28" t="n">
-        <v>7045445</v>
+        <v>7045479</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3513,11 +3518,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3651,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467384</v>
+        <v>121467368</v>
       </c>
       <c r="B30" t="n">
         <v>57354</v>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455325</v>
+        <v>455177</v>
       </c>
       <c r="R30" t="n">
-        <v>7045474</v>
+        <v>7045186</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467380</v>
+        <v>121467391</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455268</v>
+        <v>455423</v>
       </c>
       <c r="R2" t="n">
-        <v>7045458</v>
+        <v>7045462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467396</v>
+        <v>121467385</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455447</v>
+        <v>455288</v>
       </c>
       <c r="R3" t="n">
-        <v>7045445</v>
+        <v>7045273</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>121467397</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467385</v>
+        <v>121467377</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455288</v>
+        <v>455205</v>
       </c>
       <c r="R5" t="n">
-        <v>7045273</v>
+        <v>7045318</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467378</v>
+        <v>121467379</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455092</v>
+        <v>455254</v>
       </c>
       <c r="R6" t="n">
-        <v>7045431</v>
+        <v>7045408</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467379</v>
+        <v>121467384</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455254</v>
+        <v>455325</v>
       </c>
       <c r="R7" t="n">
-        <v>7045408</v>
+        <v>7045474</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467377</v>
+        <v>121467387</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455205</v>
+        <v>455393</v>
       </c>
       <c r="R8" t="n">
-        <v>7045318</v>
+        <v>7045474</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467391</v>
+        <v>121467361</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>90719</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455423</v>
+        <v>455338</v>
       </c>
       <c r="R9" t="n">
-        <v>7045462</v>
+        <v>7045372</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467388</v>
+        <v>121467368</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455401</v>
+        <v>455177</v>
       </c>
       <c r="R10" t="n">
-        <v>7045452</v>
+        <v>7045186</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467387</v>
+        <v>121467393</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455393</v>
+        <v>455424</v>
       </c>
       <c r="R11" t="n">
-        <v>7045474</v>
+        <v>7045452</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467381</v>
+        <v>121467382</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455305</v>
+        <v>455331</v>
       </c>
       <c r="R12" t="n">
-        <v>7045497</v>
+        <v>7045475</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467427</v>
+        <v>121467394</v>
       </c>
       <c r="B13" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455363</v>
+        <v>455431</v>
       </c>
       <c r="R13" t="n">
-        <v>7045446</v>
+        <v>7045439</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,6 +1923,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467393</v>
+        <v>121467375</v>
       </c>
       <c r="B14" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455424</v>
+        <v>455210</v>
       </c>
       <c r="R14" t="n">
-        <v>7045452</v>
+        <v>7045219</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467398</v>
+        <v>121467372</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455487</v>
+        <v>455187</v>
       </c>
       <c r="R15" t="n">
-        <v>7045465</v>
+        <v>7045215</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467382</v>
+        <v>121467380</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455331</v>
+        <v>455268</v>
       </c>
       <c r="R16" t="n">
-        <v>7045475</v>
+        <v>7045458</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467390</v>
+        <v>121467427</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455426</v>
+        <v>455363</v>
       </c>
       <c r="R17" t="n">
-        <v>7045466</v>
+        <v>7045446</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,11 +2351,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467425</v>
+        <v>121467386</v>
       </c>
       <c r="B18" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455347</v>
+        <v>455349</v>
       </c>
       <c r="R18" t="n">
-        <v>7045381</v>
+        <v>7045416</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,6 +2453,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467370</v>
+        <v>121467378</v>
       </c>
       <c r="B19" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455184</v>
+        <v>455092</v>
       </c>
       <c r="R19" t="n">
-        <v>7045212</v>
+        <v>7045431</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467374</v>
+        <v>121467369</v>
       </c>
       <c r="B20" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455215</v>
+        <v>455191</v>
       </c>
       <c r="R20" t="n">
-        <v>7045221</v>
+        <v>7045208</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467372</v>
+        <v>121467396</v>
       </c>
       <c r="B21" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455187</v>
+        <v>455447</v>
       </c>
       <c r="R21" t="n">
-        <v>7045215</v>
+        <v>7045445</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467384</v>
+        <v>121467388</v>
       </c>
       <c r="B22" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455325</v>
+        <v>455401</v>
       </c>
       <c r="R22" t="n">
-        <v>7045474</v>
+        <v>7045452</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467361</v>
+        <v>121467398</v>
       </c>
       <c r="B23" t="n">
-        <v>90713</v>
+        <v>57355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,21 +2928,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455338</v>
+        <v>455487</v>
       </c>
       <c r="R23" t="n">
-        <v>7045372</v>
+        <v>7045465</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,6 +2988,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467369</v>
+        <v>121467360</v>
       </c>
       <c r="B24" t="n">
-        <v>57354</v>
+        <v>90719</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455191</v>
+        <v>455351</v>
       </c>
       <c r="R24" t="n">
-        <v>7045208</v>
+        <v>7045479</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3090,11 +3095,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467394</v>
+        <v>121467423</v>
       </c>
       <c r="B25" t="n">
-        <v>57354</v>
+        <v>57371</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,16 +3137,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455431</v>
+        <v>455053</v>
       </c>
       <c r="R25" t="n">
-        <v>7045439</v>
+        <v>7045436</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467423</v>
+        <v>121467381</v>
       </c>
       <c r="B26" t="n">
-        <v>57370</v>
+        <v>57355</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,16 +3244,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455053</v>
+        <v>455305</v>
       </c>
       <c r="R26" t="n">
-        <v>7045436</v>
+        <v>7045497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467375</v>
+        <v>121467390</v>
       </c>
       <c r="B27" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455210</v>
+        <v>455426</v>
       </c>
       <c r="R27" t="n">
-        <v>7045219</v>
+        <v>7045466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467360</v>
+        <v>121467374</v>
       </c>
       <c r="B28" t="n">
-        <v>90713</v>
+        <v>57355</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455351</v>
+        <v>455215</v>
       </c>
       <c r="R28" t="n">
-        <v>7045479</v>
+        <v>7045221</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,6 +3518,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467386</v>
+        <v>121467370</v>
       </c>
       <c r="B29" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455349</v>
+        <v>455184</v>
       </c>
       <c r="R29" t="n">
-        <v>7045416</v>
+        <v>7045212</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467368</v>
+        <v>121467425</v>
       </c>
       <c r="B30" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,21 +3672,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455177</v>
+        <v>455347</v>
       </c>
       <c r="R30" t="n">
-        <v>7045186</v>
+        <v>7045381</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,11 +3732,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467391</v>
+        <v>121467396</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455423</v>
+        <v>455447</v>
       </c>
       <c r="R2" t="n">
-        <v>7045462</v>
+        <v>7045445</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467385</v>
+        <v>121467381</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455288</v>
+        <v>455305</v>
       </c>
       <c r="R3" t="n">
-        <v>7045273</v>
+        <v>7045497</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467397</v>
+        <v>121467361</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455478</v>
+        <v>455338</v>
       </c>
       <c r="R4" t="n">
-        <v>7045446</v>
+        <v>7045372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467377</v>
+        <v>121467427</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455205</v>
+        <v>455363</v>
       </c>
       <c r="R5" t="n">
-        <v>7045318</v>
+        <v>7045446</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467379</v>
+        <v>121467398</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455254</v>
+        <v>455487</v>
       </c>
       <c r="R6" t="n">
-        <v>7045408</v>
+        <v>7045465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467384</v>
+        <v>121467394</v>
       </c>
       <c r="B7" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455325</v>
+        <v>455431</v>
       </c>
       <c r="R7" t="n">
-        <v>7045474</v>
+        <v>7045439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467387</v>
+        <v>121467380</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455393</v>
+        <v>455268</v>
       </c>
       <c r="R8" t="n">
-        <v>7045474</v>
+        <v>7045458</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467361</v>
+        <v>121467369</v>
       </c>
       <c r="B9" t="n">
-        <v>90719</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455338</v>
+        <v>455191</v>
       </c>
       <c r="R9" t="n">
-        <v>7045372</v>
+        <v>7045208</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,7 +1524,7 @@
         <v>121467368</v>
       </c>
       <c r="B10" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467393</v>
+        <v>121467425</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455424</v>
+        <v>455347</v>
       </c>
       <c r="R11" t="n">
-        <v>7045452</v>
+        <v>7045381</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467382</v>
+        <v>121467378</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455331</v>
+        <v>455092</v>
       </c>
       <c r="R12" t="n">
-        <v>7045475</v>
+        <v>7045431</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467394</v>
+        <v>121467360</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455431</v>
+        <v>455351</v>
       </c>
       <c r="R13" t="n">
-        <v>7045439</v>
+        <v>7045479</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,11 +1913,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467375</v>
+        <v>121467391</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455210</v>
+        <v>455423</v>
       </c>
       <c r="R14" t="n">
-        <v>7045219</v>
+        <v>7045462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,7 +2049,7 @@
         <v>121467372</v>
       </c>
       <c r="B15" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467380</v>
+        <v>121467388</v>
       </c>
       <c r="B16" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455268</v>
+        <v>455401</v>
       </c>
       <c r="R16" t="n">
-        <v>7045458</v>
+        <v>7045452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467427</v>
+        <v>121467377</v>
       </c>
       <c r="B17" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455363</v>
+        <v>455205</v>
       </c>
       <c r="R17" t="n">
-        <v>7045446</v>
+        <v>7045318</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2336,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467386</v>
+        <v>121467379</v>
       </c>
       <c r="B18" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455349</v>
+        <v>455254</v>
       </c>
       <c r="R18" t="n">
-        <v>7045416</v>
+        <v>7045408</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467378</v>
+        <v>121467387</v>
       </c>
       <c r="B19" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2524,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455092</v>
+        <v>455393</v>
       </c>
       <c r="R19" t="n">
-        <v>7045431</v>
+        <v>7045474</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467369</v>
+        <v>121467374</v>
       </c>
       <c r="B20" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455191</v>
+        <v>455215</v>
       </c>
       <c r="R20" t="n">
-        <v>7045208</v>
+        <v>7045221</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467396</v>
+        <v>121467370</v>
       </c>
       <c r="B21" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2738,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455447</v>
+        <v>455184</v>
       </c>
       <c r="R21" t="n">
-        <v>7045445</v>
+        <v>7045212</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467388</v>
+        <v>121467385</v>
       </c>
       <c r="B22" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2845,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455401</v>
+        <v>455288</v>
       </c>
       <c r="R22" t="n">
-        <v>7045452</v>
+        <v>7045273</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467398</v>
+        <v>121467382</v>
       </c>
       <c r="B23" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2952,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455487</v>
+        <v>455331</v>
       </c>
       <c r="R23" t="n">
-        <v>7045465</v>
+        <v>7045475</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2982,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467360</v>
+        <v>121467375</v>
       </c>
       <c r="B24" t="n">
-        <v>90719</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,21 +3025,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455351</v>
+        <v>455210</v>
       </c>
       <c r="R24" t="n">
-        <v>7045479</v>
+        <v>7045219</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,6 +3085,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467423</v>
+        <v>121467397</v>
       </c>
       <c r="B25" t="n">
-        <v>57371</v>
+        <v>57356</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,16 +3132,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3161,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455053</v>
+        <v>455478</v>
       </c>
       <c r="R25" t="n">
-        <v>7045436</v>
+        <v>7045446</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3196,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467381</v>
+        <v>121467384</v>
       </c>
       <c r="B26" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3268,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455305</v>
+        <v>455325</v>
       </c>
       <c r="R26" t="n">
-        <v>7045497</v>
+        <v>7045474</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3338,7 +3333,7 @@
         <v>121467390</v>
       </c>
       <c r="B27" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3442,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467374</v>
+        <v>121467393</v>
       </c>
       <c r="B28" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3482,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455215</v>
+        <v>455424</v>
       </c>
       <c r="R28" t="n">
-        <v>7045221</v>
+        <v>7045452</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3549,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467370</v>
+        <v>121467386</v>
       </c>
       <c r="B29" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455184</v>
+        <v>455349</v>
       </c>
       <c r="R29" t="n">
-        <v>7045212</v>
+        <v>7045416</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3656,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467425</v>
+        <v>121467423</v>
       </c>
       <c r="B30" t="n">
-        <v>90737</v>
+        <v>57372</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3672,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455347</v>
+        <v>455053</v>
       </c>
       <c r="R30" t="n">
-        <v>7045381</v>
+        <v>7045436</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3732,6 +3727,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467396</v>
+        <v>121467378</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455447</v>
+        <v>455092</v>
       </c>
       <c r="R2" t="n">
-        <v>7045445</v>
+        <v>7045431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467381</v>
+        <v>121467396</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455305</v>
+        <v>455447</v>
       </c>
       <c r="R3" t="n">
-        <v>7045497</v>
+        <v>7045445</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467361</v>
+        <v>121467382</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455338</v>
+        <v>455331</v>
       </c>
       <c r="R4" t="n">
-        <v>7045372</v>
+        <v>7045475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467427</v>
+        <v>121467377</v>
       </c>
       <c r="B5" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455363</v>
+        <v>455205</v>
       </c>
       <c r="R5" t="n">
-        <v>7045446</v>
+        <v>7045318</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467398</v>
+        <v>121467368</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455487</v>
+        <v>455177</v>
       </c>
       <c r="R6" t="n">
-        <v>7045465</v>
+        <v>7045186</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467380</v>
+        <v>121467370</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1347,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455268</v>
+        <v>455184</v>
       </c>
       <c r="R8" t="n">
-        <v>7045458</v>
+        <v>7045212</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467369</v>
+        <v>121467379</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1454,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455191</v>
+        <v>455254</v>
       </c>
       <c r="R9" t="n">
-        <v>7045208</v>
+        <v>7045408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467368</v>
+        <v>121467388</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1561,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455177</v>
+        <v>455401</v>
       </c>
       <c r="R10" t="n">
-        <v>7045186</v>
+        <v>7045452</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467425</v>
+        <v>121467374</v>
       </c>
       <c r="B11" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455347</v>
+        <v>455215</v>
       </c>
       <c r="R11" t="n">
-        <v>7045381</v>
+        <v>7045221</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1714,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467378</v>
+        <v>121467391</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1770,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455092</v>
+        <v>455423</v>
       </c>
       <c r="R12" t="n">
-        <v>7045431</v>
+        <v>7045462</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467360</v>
+        <v>121467386</v>
       </c>
       <c r="B13" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455351</v>
+        <v>455349</v>
       </c>
       <c r="R13" t="n">
-        <v>7045479</v>
+        <v>7045416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1928,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467391</v>
+        <v>121467423</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,16 +1975,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1979,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455423</v>
+        <v>455053</v>
       </c>
       <c r="R14" t="n">
-        <v>7045462</v>
+        <v>7045436</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467372</v>
+        <v>121467369</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2086,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455187</v>
+        <v>455191</v>
       </c>
       <c r="R15" t="n">
-        <v>7045215</v>
+        <v>7045208</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467388</v>
+        <v>121467387</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2193,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455401</v>
+        <v>455393</v>
       </c>
       <c r="R16" t="n">
-        <v>7045452</v>
+        <v>7045474</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467377</v>
+        <v>121467381</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2300,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455205</v>
+        <v>455305</v>
       </c>
       <c r="R17" t="n">
-        <v>7045318</v>
+        <v>7045497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467379</v>
+        <v>121467361</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455254</v>
+        <v>455338</v>
       </c>
       <c r="R18" t="n">
-        <v>7045408</v>
+        <v>7045372</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,11 +2463,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467387</v>
+        <v>121467372</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2514,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455393</v>
+        <v>455187</v>
       </c>
       <c r="R19" t="n">
-        <v>7045474</v>
+        <v>7045215</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467374</v>
+        <v>121467397</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2621,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455215</v>
+        <v>455478</v>
       </c>
       <c r="R20" t="n">
-        <v>7045221</v>
+        <v>7045446</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2676,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467370</v>
+        <v>121467398</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2728,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455184</v>
+        <v>455487</v>
       </c>
       <c r="R21" t="n">
-        <v>7045212</v>
+        <v>7045465</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467385</v>
+        <v>121467360</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455288</v>
+        <v>455351</v>
       </c>
       <c r="R22" t="n">
-        <v>7045273</v>
+        <v>7045479</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2871,11 +2886,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2902,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467382</v>
+        <v>121467390</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2942,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455331</v>
+        <v>455426</v>
       </c>
       <c r="R23" t="n">
-        <v>7045475</v>
+        <v>7045466</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2992,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467375</v>
+        <v>121467427</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455210</v>
+        <v>455363</v>
       </c>
       <c r="R24" t="n">
-        <v>7045219</v>
+        <v>7045446</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,11 +3095,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,7 +3121,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467397</v>
+        <v>121467393</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3156,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455478</v>
+        <v>455424</v>
       </c>
       <c r="R25" t="n">
-        <v>7045446</v>
+        <v>7045452</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3201,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467384</v>
+        <v>121467385</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3263,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455325</v>
+        <v>455288</v>
       </c>
       <c r="R26" t="n">
-        <v>7045474</v>
+        <v>7045273</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,7 +3335,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467390</v>
+        <v>121467380</v>
       </c>
       <c r="B27" t="n">
         <v>57356</v>
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455426</v>
+        <v>455268</v>
       </c>
       <c r="R27" t="n">
-        <v>7045466</v>
+        <v>7045458</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,7 +3442,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467393</v>
+        <v>121467384</v>
       </c>
       <c r="B28" t="n">
         <v>57356</v>
@@ -3477,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455424</v>
+        <v>455325</v>
       </c>
       <c r="R28" t="n">
-        <v>7045452</v>
+        <v>7045474</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3544,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467386</v>
+        <v>121467425</v>
       </c>
       <c r="B29" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3560,21 +3565,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455349</v>
+        <v>455347</v>
       </c>
       <c r="R29" t="n">
-        <v>7045416</v>
+        <v>7045381</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3620,11 +3625,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467423</v>
+        <v>121467375</v>
       </c>
       <c r="B30" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455053</v>
+        <v>455210</v>
       </c>
       <c r="R30" t="n">
-        <v>7045436</v>
+        <v>7045219</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467378</v>
+        <v>121467386</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455092</v>
+        <v>455349</v>
       </c>
       <c r="R2" t="n">
-        <v>7045431</v>
+        <v>7045416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467396</v>
+        <v>121467391</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455447</v>
+        <v>455423</v>
       </c>
       <c r="R3" t="n">
-        <v>7045445</v>
+        <v>7045462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467382</v>
+        <v>121467427</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455331</v>
+        <v>455363</v>
       </c>
       <c r="R4" t="n">
-        <v>7045475</v>
+        <v>7045446</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467377</v>
+        <v>121467382</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455205</v>
+        <v>455331</v>
       </c>
       <c r="R5" t="n">
-        <v>7045318</v>
+        <v>7045475</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467368</v>
+        <v>121467394</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455177</v>
+        <v>455431</v>
       </c>
       <c r="R6" t="n">
-        <v>7045186</v>
+        <v>7045439</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467394</v>
+        <v>121467372</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455431</v>
+        <v>455187</v>
       </c>
       <c r="R7" t="n">
-        <v>7045439</v>
+        <v>7045215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467370</v>
+        <v>121467369</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455184</v>
+        <v>455191</v>
       </c>
       <c r="R8" t="n">
-        <v>7045212</v>
+        <v>7045208</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467379</v>
+        <v>121467388</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455254</v>
+        <v>455401</v>
       </c>
       <c r="R9" t="n">
-        <v>7045408</v>
+        <v>7045452</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467388</v>
+        <v>121467368</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1571,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455401</v>
+        <v>455177</v>
       </c>
       <c r="R10" t="n">
-        <v>7045452</v>
+        <v>7045186</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467374</v>
+        <v>121467397</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455215</v>
+        <v>455478</v>
       </c>
       <c r="R11" t="n">
-        <v>7045221</v>
+        <v>7045446</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467391</v>
+        <v>121467370</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455423</v>
+        <v>455184</v>
       </c>
       <c r="R12" t="n">
-        <v>7045462</v>
+        <v>7045212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467386</v>
+        <v>121467361</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455349</v>
+        <v>455338</v>
       </c>
       <c r="R13" t="n">
-        <v>7045416</v>
+        <v>7045372</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,11 +1923,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467423</v>
+        <v>121467425</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>90738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455053</v>
+        <v>455347</v>
       </c>
       <c r="R14" t="n">
-        <v>7045436</v>
+        <v>7045381</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,11 +2025,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467369</v>
+        <v>121467385</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2106,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455191</v>
+        <v>455288</v>
       </c>
       <c r="R15" t="n">
-        <v>7045208</v>
+        <v>7045273</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467381</v>
+        <v>121467398</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2320,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455305</v>
+        <v>455487</v>
       </c>
       <c r="R17" t="n">
-        <v>7045497</v>
+        <v>7045465</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467361</v>
+        <v>121467375</v>
       </c>
       <c r="B18" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455338</v>
+        <v>455210</v>
       </c>
       <c r="R18" t="n">
-        <v>7045372</v>
+        <v>7045219</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,6 +2448,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2479,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467372</v>
+        <v>121467381</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2529,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455187</v>
+        <v>455305</v>
       </c>
       <c r="R19" t="n">
-        <v>7045215</v>
+        <v>7045497</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467397</v>
+        <v>121467384</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2636,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455478</v>
+        <v>455325</v>
       </c>
       <c r="R20" t="n">
-        <v>7045446</v>
+        <v>7045474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2666,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467398</v>
+        <v>121467374</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2743,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455487</v>
+        <v>455215</v>
       </c>
       <c r="R21" t="n">
-        <v>7045465</v>
+        <v>7045221</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467360</v>
+        <v>121467423</v>
       </c>
       <c r="B22" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455351</v>
+        <v>455053</v>
       </c>
       <c r="R22" t="n">
-        <v>7045479</v>
+        <v>7045436</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,6 +2876,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467390</v>
+        <v>121467378</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2952,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455426</v>
+        <v>455092</v>
       </c>
       <c r="R23" t="n">
-        <v>7045466</v>
+        <v>7045431</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467427</v>
+        <v>121467390</v>
       </c>
       <c r="B24" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455363</v>
+        <v>455426</v>
       </c>
       <c r="R24" t="n">
-        <v>7045446</v>
+        <v>7045466</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,6 +3090,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,7 +3121,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467393</v>
+        <v>121467377</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455424</v>
+        <v>455205</v>
       </c>
       <c r="R25" t="n">
-        <v>7045452</v>
+        <v>7045318</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467385</v>
+        <v>121467393</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455288</v>
+        <v>455424</v>
       </c>
       <c r="R26" t="n">
-        <v>7045273</v>
+        <v>7045452</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467380</v>
+        <v>121467360</v>
       </c>
       <c r="B27" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455268</v>
+        <v>455351</v>
       </c>
       <c r="R27" t="n">
-        <v>7045458</v>
+        <v>7045479</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,11 +3411,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,7 +3437,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467384</v>
+        <v>121467396</v>
       </c>
       <c r="B28" t="n">
         <v>57356</v>
@@ -3482,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455325</v>
+        <v>455447</v>
       </c>
       <c r="R28" t="n">
-        <v>7045474</v>
+        <v>7045445</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3549,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467425</v>
+        <v>121467380</v>
       </c>
       <c r="B29" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,21 +3560,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455347</v>
+        <v>455268</v>
       </c>
       <c r="R29" t="n">
-        <v>7045381</v>
+        <v>7045458</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3625,6 +3620,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467375</v>
+        <v>121467379</v>
       </c>
       <c r="B30" t="n">
         <v>57356</v>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455210</v>
+        <v>455254</v>
       </c>
       <c r="R30" t="n">
-        <v>7045219</v>
+        <v>7045408</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467386</v>
+        <v>121467382</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455349</v>
+        <v>455331</v>
       </c>
       <c r="R2" t="n">
-        <v>7045416</v>
+        <v>7045475</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467391</v>
+        <v>121467393</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455423</v>
+        <v>455424</v>
       </c>
       <c r="R3" t="n">
-        <v>7045462</v>
+        <v>7045452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467427</v>
+        <v>121467378</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455363</v>
+        <v>455092</v>
       </c>
       <c r="R4" t="n">
-        <v>7045446</v>
+        <v>7045431</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467382</v>
+        <v>121467386</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455331</v>
+        <v>455349</v>
       </c>
       <c r="R5" t="n">
-        <v>7045475</v>
+        <v>7045416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467394</v>
+        <v>121467379</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455431</v>
+        <v>455254</v>
       </c>
       <c r="R6" t="n">
-        <v>7045439</v>
+        <v>7045408</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467372</v>
+        <v>121467394</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455187</v>
+        <v>455431</v>
       </c>
       <c r="R7" t="n">
-        <v>7045215</v>
+        <v>7045439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467388</v>
+        <v>121467381</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455401</v>
+        <v>455305</v>
       </c>
       <c r="R9" t="n">
-        <v>7045452</v>
+        <v>7045497</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467368</v>
+        <v>121467372</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1566,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455177</v>
+        <v>455187</v>
       </c>
       <c r="R10" t="n">
-        <v>7045186</v>
+        <v>7045215</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467397</v>
+        <v>121467398</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1673,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455478</v>
+        <v>455487</v>
       </c>
       <c r="R11" t="n">
-        <v>7045446</v>
+        <v>7045465</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467370</v>
+        <v>121467361</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455184</v>
+        <v>455338</v>
       </c>
       <c r="R12" t="n">
-        <v>7045212</v>
+        <v>7045372</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1821,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467361</v>
+        <v>121467380</v>
       </c>
       <c r="B13" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455338</v>
+        <v>455268</v>
       </c>
       <c r="R13" t="n">
-        <v>7045372</v>
+        <v>7045458</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,6 +1923,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467425</v>
+        <v>121467423</v>
       </c>
       <c r="B14" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455347</v>
+        <v>455053</v>
       </c>
       <c r="R14" t="n">
-        <v>7045381</v>
+        <v>7045436</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +2030,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467385</v>
+        <v>121467387</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2091,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455288</v>
+        <v>455393</v>
       </c>
       <c r="R15" t="n">
-        <v>7045273</v>
+        <v>7045474</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467387</v>
+        <v>121467397</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2198,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455393</v>
+        <v>455478</v>
       </c>
       <c r="R16" t="n">
-        <v>7045474</v>
+        <v>7045446</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467398</v>
+        <v>121467388</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2305,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455487</v>
+        <v>455401</v>
       </c>
       <c r="R17" t="n">
-        <v>7045465</v>
+        <v>7045452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467375</v>
+        <v>121467385</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2412,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455210</v>
+        <v>455288</v>
       </c>
       <c r="R18" t="n">
-        <v>7045219</v>
+        <v>7045273</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467381</v>
+        <v>121467368</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2519,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455305</v>
+        <v>455177</v>
       </c>
       <c r="R19" t="n">
-        <v>7045497</v>
+        <v>7045186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467384</v>
+        <v>121467377</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2626,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455325</v>
+        <v>455205</v>
       </c>
       <c r="R20" t="n">
-        <v>7045474</v>
+        <v>7045318</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467374</v>
+        <v>121467384</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2733,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455215</v>
+        <v>455325</v>
       </c>
       <c r="R21" t="n">
-        <v>7045221</v>
+        <v>7045474</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467423</v>
+        <v>121467396</v>
       </c>
       <c r="B22" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,16 +2826,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2840,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455053</v>
+        <v>455447</v>
       </c>
       <c r="R22" t="n">
-        <v>7045436</v>
+        <v>7045445</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2890,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2917,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467378</v>
+        <v>121467375</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2947,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455092</v>
+        <v>455210</v>
       </c>
       <c r="R23" t="n">
-        <v>7045431</v>
+        <v>7045219</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467390</v>
+        <v>121467427</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455426</v>
+        <v>455363</v>
       </c>
       <c r="R24" t="n">
-        <v>7045466</v>
+        <v>7045446</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3090,11 +3100,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3126,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467377</v>
+        <v>121467360</v>
       </c>
       <c r="B25" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455205</v>
+        <v>455351</v>
       </c>
       <c r="R25" t="n">
-        <v>7045318</v>
+        <v>7045479</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,11 +3202,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467393</v>
+        <v>121467391</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455424</v>
+        <v>455423</v>
       </c>
       <c r="R26" t="n">
-        <v>7045452</v>
+        <v>7045462</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467360</v>
+        <v>121467390</v>
       </c>
       <c r="B27" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455351</v>
+        <v>455426</v>
       </c>
       <c r="R27" t="n">
-        <v>7045479</v>
+        <v>7045466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,6 +3411,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467396</v>
+        <v>121467425</v>
       </c>
       <c r="B28" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3453,21 +3458,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3477,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455447</v>
+        <v>455347</v>
       </c>
       <c r="R28" t="n">
-        <v>7045445</v>
+        <v>7045381</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3513,11 +3518,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,7 +3544,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467380</v>
+        <v>121467374</v>
       </c>
       <c r="B29" t="n">
         <v>57356</v>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455268</v>
+        <v>455215</v>
       </c>
       <c r="R29" t="n">
-        <v>7045458</v>
+        <v>7045221</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467379</v>
+        <v>121467370</v>
       </c>
       <c r="B30" t="n">
         <v>57356</v>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455254</v>
+        <v>455184</v>
       </c>
       <c r="R30" t="n">
-        <v>7045408</v>
+        <v>7045212</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -3126,10 +3126,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467360</v>
+        <v>121467391</v>
       </c>
       <c r="B25" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455351</v>
+        <v>455423</v>
       </c>
       <c r="R25" t="n">
-        <v>7045479</v>
+        <v>7045462</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,6 +3202,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,7 +3233,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467391</v>
+        <v>121467390</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3268,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455423</v>
+        <v>455426</v>
       </c>
       <c r="R26" t="n">
-        <v>7045462</v>
+        <v>7045466</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3313,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3340,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467390</v>
+        <v>121467360</v>
       </c>
       <c r="B27" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,21 +3356,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455426</v>
+        <v>455351</v>
       </c>
       <c r="R27" t="n">
-        <v>7045466</v>
+        <v>7045479</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,11 +3416,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467423</v>
+        <v>121467387</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,16 +1970,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455053</v>
+        <v>455393</v>
       </c>
       <c r="R14" t="n">
-        <v>7045436</v>
+        <v>7045474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467387</v>
+        <v>121467397</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455393</v>
+        <v>455478</v>
       </c>
       <c r="R15" t="n">
-        <v>7045474</v>
+        <v>7045446</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467397</v>
+        <v>121467423</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,16 +2184,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455478</v>
+        <v>455053</v>
       </c>
       <c r="R16" t="n">
-        <v>7045446</v>
+        <v>7045436</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3126,10 +3126,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467391</v>
+        <v>121467360</v>
       </c>
       <c r="B25" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455423</v>
+        <v>455351</v>
       </c>
       <c r="R25" t="n">
-        <v>7045462</v>
+        <v>7045479</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,11 +3202,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467390</v>
+        <v>121467391</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3273,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455426</v>
+        <v>455423</v>
       </c>
       <c r="R26" t="n">
-        <v>7045466</v>
+        <v>7045462</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3308,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467360</v>
+        <v>121467390</v>
       </c>
       <c r="B27" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3356,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3380,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455351</v>
+        <v>455426</v>
       </c>
       <c r="R27" t="n">
-        <v>7045479</v>
+        <v>7045466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3416,6 +3411,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467382</v>
+        <v>121467372</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455331</v>
+        <v>455187</v>
       </c>
       <c r="R2" t="n">
-        <v>7045475</v>
+        <v>7045215</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467393</v>
+        <v>121467381</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455424</v>
+        <v>455305</v>
       </c>
       <c r="R3" t="n">
-        <v>7045452</v>
+        <v>7045497</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467378</v>
+        <v>121467370</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455092</v>
+        <v>455184</v>
       </c>
       <c r="R4" t="n">
-        <v>7045431</v>
+        <v>7045212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467386</v>
+        <v>121467382</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455349</v>
+        <v>455331</v>
       </c>
       <c r="R5" t="n">
-        <v>7045416</v>
+        <v>7045475</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>121467379</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467394</v>
+        <v>121467393</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455431</v>
+        <v>455424</v>
       </c>
       <c r="R7" t="n">
-        <v>7045439</v>
+        <v>7045452</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467369</v>
+        <v>121467384</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455191</v>
+        <v>455325</v>
       </c>
       <c r="R8" t="n">
-        <v>7045208</v>
+        <v>7045474</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467381</v>
+        <v>121467397</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455305</v>
+        <v>455478</v>
       </c>
       <c r="R9" t="n">
-        <v>7045497</v>
+        <v>7045446</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467372</v>
+        <v>121467360</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455187</v>
+        <v>455351</v>
       </c>
       <c r="R10" t="n">
-        <v>7045215</v>
+        <v>7045479</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,11 +1607,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467398</v>
+        <v>121467374</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455487</v>
+        <v>455215</v>
       </c>
       <c r="R11" t="n">
-        <v>7045465</v>
+        <v>7045221</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467361</v>
+        <v>121467378</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455338</v>
+        <v>455092</v>
       </c>
       <c r="R12" t="n">
-        <v>7045372</v>
+        <v>7045431</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467380</v>
+        <v>121467398</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455268</v>
+        <v>455487</v>
       </c>
       <c r="R13" t="n">
-        <v>7045458</v>
+        <v>7045465</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467387</v>
+        <v>121467377</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455393</v>
+        <v>455205</v>
       </c>
       <c r="R14" t="n">
-        <v>7045474</v>
+        <v>7045318</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467397</v>
+        <v>121467425</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455478</v>
+        <v>455347</v>
       </c>
       <c r="R15" t="n">
-        <v>7045446</v>
+        <v>7045381</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,11 +2137,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467423</v>
+        <v>121467386</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,16 +2179,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455053</v>
+        <v>455349</v>
       </c>
       <c r="R16" t="n">
-        <v>7045436</v>
+        <v>7045416</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467388</v>
+        <v>121467391</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455401</v>
+        <v>455423</v>
       </c>
       <c r="R17" t="n">
-        <v>7045452</v>
+        <v>7045462</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467385</v>
+        <v>121467427</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455288</v>
+        <v>455363</v>
       </c>
       <c r="R18" t="n">
-        <v>7045273</v>
+        <v>7045446</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,11 +2453,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467368</v>
+        <v>121467385</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455177</v>
+        <v>455288</v>
       </c>
       <c r="R19" t="n">
-        <v>7045186</v>
+        <v>7045273</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2559,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467377</v>
+        <v>121467375</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2636,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455205</v>
+        <v>455210</v>
       </c>
       <c r="R20" t="n">
-        <v>7045318</v>
+        <v>7045219</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467384</v>
+        <v>121467369</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2743,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455325</v>
+        <v>455191</v>
       </c>
       <c r="R21" t="n">
-        <v>7045474</v>
+        <v>7045208</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467396</v>
+        <v>121467423</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>57373</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,16 +2816,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2850,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455447</v>
+        <v>455053</v>
       </c>
       <c r="R22" t="n">
-        <v>7045445</v>
+        <v>7045436</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467375</v>
+        <v>121467396</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455210</v>
+        <v>455447</v>
       </c>
       <c r="R23" t="n">
-        <v>7045219</v>
+        <v>7045445</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467427</v>
+        <v>121467388</v>
       </c>
       <c r="B24" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3040,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455363</v>
+        <v>455401</v>
       </c>
       <c r="R24" t="n">
-        <v>7045446</v>
+        <v>7045452</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,6 +3090,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467360</v>
+        <v>121467368</v>
       </c>
       <c r="B25" t="n">
-        <v>90720</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,21 +3137,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455351</v>
+        <v>455177</v>
       </c>
       <c r="R25" t="n">
-        <v>7045479</v>
+        <v>7045186</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,6 +3197,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467391</v>
+        <v>121467387</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455423</v>
+        <v>455393</v>
       </c>
       <c r="R26" t="n">
-        <v>7045462</v>
+        <v>7045474</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467390</v>
+        <v>121467380</v>
       </c>
       <c r="B27" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455426</v>
+        <v>455268</v>
       </c>
       <c r="R27" t="n">
-        <v>7045466</v>
+        <v>7045458</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467425</v>
+        <v>121467394</v>
       </c>
       <c r="B28" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455347</v>
+        <v>455431</v>
       </c>
       <c r="R28" t="n">
-        <v>7045381</v>
+        <v>7045439</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,6 +3518,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467374</v>
+        <v>121467361</v>
       </c>
       <c r="B29" t="n">
-        <v>57356</v>
+        <v>90728</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3560,21 +3565,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455215</v>
+        <v>455338</v>
       </c>
       <c r="R29" t="n">
-        <v>7045221</v>
+        <v>7045372</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3620,11 +3625,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467370</v>
+        <v>121467390</v>
       </c>
       <c r="B30" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455184</v>
+        <v>455426</v>
       </c>
       <c r="R30" t="n">
-        <v>7045212</v>
+        <v>7045466</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467360</v>
+        <v>121467374</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455351</v>
+        <v>455215</v>
       </c>
       <c r="R10" t="n">
-        <v>7045479</v>
+        <v>7045221</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,6 +1607,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467374</v>
+        <v>121467360</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455215</v>
+        <v>455351</v>
       </c>
       <c r="R11" t="n">
-        <v>7045221</v>
+        <v>7045479</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1714,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3549,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467361</v>
+        <v>121467390</v>
       </c>
       <c r="B29" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,21 +3565,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455338</v>
+        <v>455426</v>
       </c>
       <c r="R29" t="n">
-        <v>7045372</v>
+        <v>7045466</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3625,6 +3625,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467390</v>
+        <v>121467361</v>
       </c>
       <c r="B30" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,21 +3672,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455426</v>
+        <v>455338</v>
       </c>
       <c r="R30" t="n">
-        <v>7045466</v>
+        <v>7045372</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,11 +3732,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467374</v>
+        <v>121467360</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455215</v>
+        <v>455351</v>
       </c>
       <c r="R10" t="n">
-        <v>7045221</v>
+        <v>7045479</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,11 +1607,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467360</v>
+        <v>121467374</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455351</v>
+        <v>455215</v>
       </c>
       <c r="R11" t="n">
-        <v>7045479</v>
+        <v>7045221</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467425</v>
+        <v>121467391</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455347</v>
+        <v>455423</v>
       </c>
       <c r="R2" t="n">
-        <v>7045381</v>
+        <v>7045462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467384</v>
+        <v>121467423</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455325</v>
+        <v>455053</v>
       </c>
       <c r="R3" t="n">
-        <v>7045474</v>
+        <v>7045436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467394</v>
+        <v>121467388</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455431</v>
+        <v>455401</v>
       </c>
       <c r="R4" t="n">
-        <v>7045439</v>
+        <v>7045452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467398</v>
+        <v>121467369</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455487</v>
+        <v>455191</v>
       </c>
       <c r="R5" t="n">
-        <v>7045465</v>
+        <v>7045208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467382</v>
+        <v>121467381</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455331</v>
+        <v>455305</v>
       </c>
       <c r="R6" t="n">
-        <v>7045475</v>
+        <v>7045497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467388</v>
+        <v>121467375</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455401</v>
+        <v>455210</v>
       </c>
       <c r="R7" t="n">
-        <v>7045452</v>
+        <v>7045219</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467368</v>
+        <v>121467377</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455177</v>
+        <v>455205</v>
       </c>
       <c r="R8" t="n">
-        <v>7045186</v>
+        <v>7045318</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467370</v>
+        <v>121467379</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455184</v>
+        <v>455254</v>
       </c>
       <c r="R9" t="n">
-        <v>7045212</v>
+        <v>7045408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467396</v>
+        <v>121467390</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1566,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455447</v>
+        <v>455426</v>
       </c>
       <c r="R10" t="n">
-        <v>7045445</v>
+        <v>7045466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467385</v>
+        <v>121467397</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1673,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455288</v>
+        <v>455478</v>
       </c>
       <c r="R11" t="n">
-        <v>7045273</v>
+        <v>7045446</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467387</v>
+        <v>121467425</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455393</v>
+        <v>455347</v>
       </c>
       <c r="R12" t="n">
-        <v>7045474</v>
+        <v>7045381</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1821,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467423</v>
+        <v>121467372</v>
       </c>
       <c r="B13" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,16 +1863,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455053</v>
+        <v>455187</v>
       </c>
       <c r="R13" t="n">
-        <v>7045436</v>
+        <v>7045215</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467393</v>
+        <v>121467398</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455424</v>
+        <v>455487</v>
       </c>
       <c r="R14" t="n">
-        <v>7045452</v>
+        <v>7045465</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467375</v>
+        <v>121467394</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455210</v>
+        <v>455431</v>
       </c>
       <c r="R15" t="n">
-        <v>7045219</v>
+        <v>7045439</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467381</v>
+        <v>121467380</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455305</v>
+        <v>455268</v>
       </c>
       <c r="R16" t="n">
-        <v>7045497</v>
+        <v>7045458</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467360</v>
+        <v>121467387</v>
       </c>
       <c r="B17" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455351</v>
+        <v>455393</v>
       </c>
       <c r="R17" t="n">
-        <v>7045479</v>
+        <v>7045474</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2351,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467378</v>
+        <v>121467374</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2417,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455092</v>
+        <v>455215</v>
       </c>
       <c r="R18" t="n">
-        <v>7045431</v>
+        <v>7045221</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467372</v>
+        <v>121467361</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455187</v>
+        <v>455338</v>
       </c>
       <c r="R19" t="n">
-        <v>7045215</v>
+        <v>7045372</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,11 +2565,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467427</v>
+        <v>121467385</v>
       </c>
       <c r="B20" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455363</v>
+        <v>455288</v>
       </c>
       <c r="R20" t="n">
-        <v>7045446</v>
+        <v>7045273</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,6 +2667,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467397</v>
+        <v>121467384</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455478</v>
+        <v>455325</v>
       </c>
       <c r="R21" t="n">
-        <v>7045446</v>
+        <v>7045474</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467386</v>
+        <v>121467370</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455349</v>
+        <v>455184</v>
       </c>
       <c r="R22" t="n">
-        <v>7045416</v>
+        <v>7045212</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467377</v>
+        <v>121467386</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -2947,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455205</v>
+        <v>455349</v>
       </c>
       <c r="R23" t="n">
-        <v>7045318</v>
+        <v>7045416</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3019,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467369</v>
+        <v>121467396</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3054,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455191</v>
+        <v>455447</v>
       </c>
       <c r="R24" t="n">
-        <v>7045208</v>
+        <v>7045445</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3126,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467391</v>
+        <v>121467382</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3161,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455423</v>
+        <v>455331</v>
       </c>
       <c r="R25" t="n">
-        <v>7045462</v>
+        <v>7045475</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,7 +3233,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467379</v>
+        <v>121467393</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3268,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455254</v>
+        <v>455424</v>
       </c>
       <c r="R26" t="n">
-        <v>7045408</v>
+        <v>7045452</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,7 +3340,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467380</v>
+        <v>121467368</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3375,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455268</v>
+        <v>455177</v>
       </c>
       <c r="R27" t="n">
-        <v>7045458</v>
+        <v>7045186</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,7 +3420,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,10 +3447,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467361</v>
+        <v>121467427</v>
       </c>
       <c r="B28" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,21 +3463,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3482,10 +3487,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455338</v>
+        <v>455363</v>
       </c>
       <c r="R28" t="n">
-        <v>7045372</v>
+        <v>7045446</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3544,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467374</v>
+        <v>121467360</v>
       </c>
       <c r="B29" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3560,21 +3565,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455215</v>
+        <v>455351</v>
       </c>
       <c r="R29" t="n">
-        <v>7045221</v>
+        <v>7045479</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3620,11 +3625,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467390</v>
+        <v>121467378</v>
       </c>
       <c r="B30" t="n">
         <v>57357</v>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455426</v>
+        <v>455092</v>
       </c>
       <c r="R30" t="n">
-        <v>7045466</v>
+        <v>7045431</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -2489,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467361</v>
+        <v>121467385</v>
       </c>
       <c r="B19" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455338</v>
+        <v>455288</v>
       </c>
       <c r="R19" t="n">
-        <v>7045372</v>
+        <v>7045273</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,6 +2565,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467385</v>
+        <v>121467384</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2631,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455288</v>
+        <v>455325</v>
       </c>
       <c r="R20" t="n">
-        <v>7045273</v>
+        <v>7045474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467384</v>
+        <v>121467370</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2738,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455325</v>
+        <v>455184</v>
       </c>
       <c r="R21" t="n">
-        <v>7045474</v>
+        <v>7045212</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467370</v>
+        <v>121467361</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455184</v>
+        <v>455338</v>
       </c>
       <c r="R22" t="n">
-        <v>7045212</v>
+        <v>7045372</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,11 +2886,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467391</v>
+        <v>121467381</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455423</v>
+        <v>455305</v>
       </c>
       <c r="R2" t="n">
-        <v>7045462</v>
+        <v>7045497</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467423</v>
+        <v>121467425</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455053</v>
+        <v>455347</v>
       </c>
       <c r="R3" t="n">
-        <v>7045436</v>
+        <v>7045381</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467388</v>
+        <v>121467382</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455401</v>
+        <v>455331</v>
       </c>
       <c r="R4" t="n">
-        <v>7045452</v>
+        <v>7045475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467369</v>
+        <v>121467388</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455191</v>
+        <v>455401</v>
       </c>
       <c r="R5" t="n">
-        <v>7045208</v>
+        <v>7045452</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467381</v>
+        <v>121467393</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455305</v>
+        <v>455424</v>
       </c>
       <c r="R6" t="n">
-        <v>7045497</v>
+        <v>7045452</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467377</v>
+        <v>121467398</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455205</v>
+        <v>455487</v>
       </c>
       <c r="R8" t="n">
-        <v>7045318</v>
+        <v>7045465</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467379</v>
+        <v>121467423</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,16 +1435,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455254</v>
+        <v>455053</v>
       </c>
       <c r="R9" t="n">
-        <v>7045408</v>
+        <v>7045436</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467390</v>
+        <v>121467386</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1571,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455426</v>
+        <v>455349</v>
       </c>
       <c r="R10" t="n">
-        <v>7045466</v>
+        <v>7045416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467397</v>
+        <v>121467394</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455478</v>
+        <v>455431</v>
       </c>
       <c r="R11" t="n">
-        <v>7045446</v>
+        <v>7045439</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467425</v>
+        <v>121467360</v>
       </c>
       <c r="B12" t="n">
-        <v>90746</v>
+        <v>90728</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455347</v>
+        <v>455351</v>
       </c>
       <c r="R12" t="n">
-        <v>7045381</v>
+        <v>7045479</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467372</v>
+        <v>121467370</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455187</v>
+        <v>455184</v>
       </c>
       <c r="R13" t="n">
-        <v>7045215</v>
+        <v>7045212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467398</v>
+        <v>121467384</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455487</v>
+        <v>455325</v>
       </c>
       <c r="R14" t="n">
-        <v>7045465</v>
+        <v>7045474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467394</v>
+        <v>121467390</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455431</v>
+        <v>455426</v>
       </c>
       <c r="R15" t="n">
-        <v>7045439</v>
+        <v>7045466</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467380</v>
+        <v>121467391</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455268</v>
+        <v>455423</v>
       </c>
       <c r="R16" t="n">
-        <v>7045458</v>
+        <v>7045462</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467374</v>
+        <v>121467396</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455215</v>
+        <v>455447</v>
       </c>
       <c r="R18" t="n">
-        <v>7045221</v>
+        <v>7045445</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467385</v>
+        <v>121467397</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455288</v>
+        <v>455478</v>
       </c>
       <c r="R19" t="n">
-        <v>7045273</v>
+        <v>7045446</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467384</v>
+        <v>121467368</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2636,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455325</v>
+        <v>455177</v>
       </c>
       <c r="R20" t="n">
-        <v>7045474</v>
+        <v>7045186</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2671,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467370</v>
+        <v>121467372</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2743,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455184</v>
+        <v>455187</v>
       </c>
       <c r="R21" t="n">
-        <v>7045212</v>
+        <v>7045215</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2912,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467386</v>
+        <v>121467377</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -2952,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455349</v>
+        <v>455205</v>
       </c>
       <c r="R23" t="n">
-        <v>7045416</v>
+        <v>7045318</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467396</v>
+        <v>121467374</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3059,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455447</v>
+        <v>455215</v>
       </c>
       <c r="R24" t="n">
-        <v>7045445</v>
+        <v>7045221</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,7 +3121,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467382</v>
+        <v>121467369</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3166,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455331</v>
+        <v>455191</v>
       </c>
       <c r="R25" t="n">
-        <v>7045475</v>
+        <v>7045208</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3201,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467393</v>
+        <v>121467427</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3249,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3273,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455424</v>
+        <v>455363</v>
       </c>
       <c r="R26" t="n">
-        <v>7045452</v>
+        <v>7045446</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3309,11 +3304,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467368</v>
+        <v>121467379</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3380,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455177</v>
+        <v>455254</v>
       </c>
       <c r="R27" t="n">
-        <v>7045186</v>
+        <v>7045408</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467427</v>
+        <v>121467380</v>
       </c>
       <c r="B28" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,21 +3453,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3487,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455363</v>
+        <v>455268</v>
       </c>
       <c r="R28" t="n">
-        <v>7045446</v>
+        <v>7045458</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3523,6 +3513,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121467360</v>
+        <v>121467378</v>
       </c>
       <c r="B29" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,21 +3560,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455351</v>
+        <v>455092</v>
       </c>
       <c r="R29" t="n">
-        <v>7045479</v>
+        <v>7045431</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3625,6 +3620,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121467378</v>
+        <v>121467385</v>
       </c>
       <c r="B30" t="n">
         <v>57357</v>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455092</v>
+        <v>455288</v>
       </c>
       <c r="R30" t="n">
-        <v>7045431</v>
+        <v>7045273</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467381</v>
+        <v>121467360</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455305</v>
+        <v>455351</v>
       </c>
       <c r="R2" t="n">
-        <v>7045497</v>
+        <v>7045479</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467425</v>
+        <v>121467361</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455347</v>
+        <v>455338</v>
       </c>
       <c r="R3" t="n">
-        <v>7045381</v>
+        <v>7045372</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,32 +869,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467382</v>
+        <v>121467423</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455331</v>
+        <v>455053</v>
       </c>
       <c r="R4" t="n">
-        <v>7045475</v>
+        <v>7045436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121467388</v>
+        <v>121467368</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455401</v>
+        <v>455177</v>
       </c>
       <c r="R5" t="n">
-        <v>7045452</v>
+        <v>7045186</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,15 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121467393</v>
+        <v>121467369</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455424</v>
+        <v>455191</v>
       </c>
       <c r="R6" t="n">
-        <v>7045452</v>
+        <v>7045208</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121467375</v>
+        <v>121467370</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455210</v>
+        <v>455184</v>
       </c>
       <c r="R7" t="n">
-        <v>7045219</v>
+        <v>7045212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121467398</v>
+        <v>121467372</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455487</v>
+        <v>455187</v>
       </c>
       <c r="R8" t="n">
-        <v>7045465</v>
+        <v>7045215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,15 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121467423</v>
+        <v>121467374</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,16 +1390,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1459,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455053</v>
+        <v>455215</v>
       </c>
       <c r="R9" t="n">
-        <v>7045436</v>
+        <v>7045221</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,15 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121467386</v>
+        <v>121467375</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455349</v>
+        <v>455210</v>
       </c>
       <c r="R10" t="n">
-        <v>7045416</v>
+        <v>7045219</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,15 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121467394</v>
+        <v>121467377</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455431</v>
+        <v>455205</v>
       </c>
       <c r="R11" t="n">
-        <v>7045439</v>
+        <v>7045318</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121467360</v>
+        <v>121467378</v>
       </c>
       <c r="B12" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455351</v>
+        <v>455092</v>
       </c>
       <c r="R12" t="n">
-        <v>7045479</v>
+        <v>7045431</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,15 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121467370</v>
+        <v>121467379</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455184</v>
+        <v>455254</v>
       </c>
       <c r="R13" t="n">
-        <v>7045212</v>
+        <v>7045408</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,15 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121467384</v>
+        <v>121467380</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455325</v>
+        <v>455268</v>
       </c>
       <c r="R14" t="n">
-        <v>7045474</v>
+        <v>7045458</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,15 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121467390</v>
+        <v>121467381</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455426</v>
+        <v>455305</v>
       </c>
       <c r="R15" t="n">
-        <v>7045466</v>
+        <v>7045497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,15 +2093,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121467391</v>
+        <v>121467382</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455423</v>
+        <v>455331</v>
       </c>
       <c r="R16" t="n">
-        <v>7045462</v>
+        <v>7045475</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,15 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121467387</v>
+        <v>121467384</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,7 +2230,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455393</v>
+        <v>455325</v>
       </c>
       <c r="R17" t="n">
         <v>7045474</v>
@@ -2377,15 +2297,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121467396</v>
+        <v>121467385</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455447</v>
+        <v>455288</v>
       </c>
       <c r="R18" t="n">
-        <v>7045445</v>
+        <v>7045273</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,15 +2399,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121467397</v>
+        <v>121467386</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455478</v>
+        <v>455349</v>
       </c>
       <c r="R19" t="n">
-        <v>7045446</v>
+        <v>7045416</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2474,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,15 +2501,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121467368</v>
+        <v>121467387</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455177</v>
+        <v>455393</v>
       </c>
       <c r="R20" t="n">
-        <v>7045186</v>
+        <v>7045474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2576,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,15 +2603,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121467372</v>
+        <v>121467388</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,10 +2638,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455187</v>
+        <v>455401</v>
       </c>
       <c r="R21" t="n">
-        <v>7045215</v>
+        <v>7045452</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,15 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121467361</v>
+        <v>121467390</v>
       </c>
       <c r="B22" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455338</v>
+        <v>455426</v>
       </c>
       <c r="R22" t="n">
-        <v>7045372</v>
+        <v>7045466</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,6 +2776,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,15 +2807,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121467377</v>
+        <v>121467391</v>
       </c>
       <c r="B23" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2947,10 +2842,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455205</v>
+        <v>455423</v>
       </c>
       <c r="R23" t="n">
-        <v>7045318</v>
+        <v>7045462</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2882,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,15 +2909,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121467374</v>
+        <v>121467393</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,10 +2944,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455215</v>
+        <v>455424</v>
       </c>
       <c r="R24" t="n">
-        <v>7045221</v>
+        <v>7045452</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,15 +3011,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121467369</v>
+        <v>121467394</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,10 +3046,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455191</v>
+        <v>455431</v>
       </c>
       <c r="R25" t="n">
-        <v>7045208</v>
+        <v>7045439</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,15 +3113,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121467427</v>
+        <v>121467396</v>
       </c>
       <c r="B26" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,21 +3124,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3148,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455363</v>
+        <v>455447</v>
       </c>
       <c r="R26" t="n">
-        <v>7045446</v>
+        <v>7045445</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3304,6 +3184,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,15 +3215,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121467379</v>
+        <v>121467397</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3370,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455254</v>
+        <v>455478</v>
       </c>
       <c r="R27" t="n">
-        <v>7045408</v>
+        <v>7045446</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3290,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,15 +3317,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121467380</v>
+        <v>121467398</v>
       </c>
       <c r="B28" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,10 +3352,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455268</v>
+        <v>455487</v>
       </c>
       <c r="R28" t="n">
-        <v>7045458</v>
+        <v>7045465</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3541,220 +3416,6 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>121467378</v>
-      </c>
-      <c r="B29" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Storflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>455092</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7045431</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>121467385</v>
-      </c>
-      <c r="B30" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Storflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>455288</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7045273</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56312-2024 artfynd.xlsx
+++ b/artfynd/A 56312-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467360</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467361</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467423</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467368</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467369</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467370</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467372</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467374</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467375</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467377</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467378</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467379</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467380</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467381</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467382</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2294,6 +2374,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467384</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2396,6 +2481,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467385</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2498,6 +2588,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467386</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2600,6 +2695,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467387</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2702,6 +2802,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467388</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2804,6 +2909,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467390</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2906,6 +3016,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467391</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3008,6 +3123,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467393</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3110,6 +3230,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467394</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3212,6 +3337,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467396</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3314,6 +3444,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467397</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3416,8 +3551,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467398</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>